--- a/datos/registros-aedes.xlsx
+++ b/datos/registros-aedes.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K2"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -513,6 +513,51 @@
         <v>11276</v>
       </c>
       <c r="K2" t="inlineStr">
+        <is>
+          <t>No</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-05-28</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>21:52:53</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>54</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>328.12</v>
+      </c>
+      <c r="F3" t="n">
+        <v>-20.7</v>
+      </c>
+      <c r="G3" t="n">
+        <v>0</v>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>617.2 Hz | 1023.4 Hz | 1281.2 Hz</t>
+        </is>
+      </c>
+      <c r="I3" t="n">
+        <v>2547</v>
+      </c>
+      <c r="J3" t="n">
+        <v>11777</v>
+      </c>
+      <c r="K3" t="inlineStr">
         <is>
           <t>No</t>
         </is>
